--- a/artfynd/A 14265-2025 artfynd.xlsx
+++ b/artfynd/A 14265-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>54889192</v>
+        <v>54888991</v>
       </c>
       <c r="B2" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -725,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578070.3206744761</v>
+        <v>578042</v>
       </c>
       <c r="R2" t="n">
-        <v>6627853.596639764</v>
+        <v>6627858</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -758,19 +753,9 @@
           <t>2015-08-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-08-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,7 +770,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>lövskogsbryn</t>
+          <t>äldre barrblandskog</t>
         </is>
       </c>
       <c r="AN2" t="n">
@@ -811,15 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>54888991</v>
+        <v>54888995</v>
       </c>
       <c r="B3" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -846,7 +826,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -861,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578042.4895871886</v>
+        <v>578040</v>
       </c>
       <c r="R3" t="n">
-        <v>6627857.545846307</v>
+        <v>6627841</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -894,19 +874,9 @@
           <t>2015-08-20</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2015-08-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,7 +891,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>äldre barrblandskog</t>
+          <t>barrblandskogsbryn</t>
         </is>
       </c>
       <c r="AN3" t="n">
@@ -950,12 +920,7 @@
         <v>54889177</v>
       </c>
       <c r="B4" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578056.6122535081</v>
+        <v>578057</v>
       </c>
       <c r="R4" t="n">
-        <v>6627833.666546944</v>
+        <v>6627834</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1030,19 +995,9 @@
           <t>2015-08-20</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2015-08-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1083,15 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>54889237</v>
+        <v>54889192</v>
       </c>
       <c r="B5" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,14 +1079,14 @@
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Grans, Svanå, Vstm</t>
+          <t>Grans, V, Svanå, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578129.2294001229</v>
+        <v>578070</v>
       </c>
       <c r="R5" t="n">
-        <v>6627931.387490834</v>
+        <v>6627854</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1166,19 +1116,9 @@
           <t>2015-08-20</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2015-08-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1193,7 +1133,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>gammal barrblandskog</t>
+          <t>lövskogsbryn</t>
         </is>
       </c>
       <c r="AN5" t="n">
@@ -1219,67 +1159,58 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>55925918</v>
+        <v>54889237</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Grans, Svanå (knärot), Vstm</t>
+          <t>Grans, Svanå, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578097.4068213816</v>
+        <v>578129</v>
       </c>
       <c r="R6" t="n">
-        <v>6627933.237815966</v>
+        <v>6627931</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1301,54 +1232,43 @@
           <t>Haraker</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>U-Väs-0506</t>
-        </is>
-      </c>
       <c r="Y6" t="inlineStr">
         <is>
           <t>2015-08-20</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2015-08-20</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Koord: 1532920/6629279/5m.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
           <t>gammal barrblandskog</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal, grov tall</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Einar Marklund</t>
+          <t>Henrik Berg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -1356,76 +1276,52 @@
           <t>Henrik Berg</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>54889223</v>
+        <v>68188660</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grans, Svanå, Vstm</t>
+          <t>Svanå, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578107.5241483649</v>
+        <v>578057</v>
       </c>
       <c r="R7" t="n">
-        <v>6627931.939197989</v>
+        <v>6627830</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1449,22 +1345,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2015-08-20</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2015-08-20</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-10-11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1475,74 +1361,79 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>gammal barrblandskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Henrik Berg</t>
+          <t>Kirsi Jokinen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Henrik Berg</t>
+          <t>Kirsi Jokinen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122589604</v>
+        <v>54889223</v>
       </c>
       <c r="B8" t="n">
-        <v>100631</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Grans, Svanå, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578073</v>
+        <v>578108</v>
       </c>
       <c r="R8" t="n">
-        <v>6627838</v>
+        <v>6627932</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1566,12 +1457,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2015-08-20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2015-08-20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1585,21 +1476,253 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Blandskog</t>
+          <t>gammal barrblandskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
+          <t>Henrik Berg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Henrik Berg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>55925918</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Grans, Svanå (knärot), Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>578097</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6627933</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Haraker</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>U-Väs-0506</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2015-08-20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2015-08-20</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Koord: 1532920/6629279/5m.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>gammal barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Einar Marklund</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Henrik Berg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122589604</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Grans, Svanå, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>578073</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6627838</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Haraker</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-09-08</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Bengt Stridh</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Bengt Stridh, Dennis JP Nyström, Josefin Kjellberg</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Josefin Kjellberg, Dennis JP Nyström, Bengt Stridh</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14265-2025 artfynd.xlsx
+++ b/artfynd/A 14265-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54888991</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,6 +924,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54888995</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1035,6 +1050,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54889177</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1156,6 +1176,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54889192</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1277,6 +1302,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54889237</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1374,6 +1404,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68188660</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1491,6 +1526,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54889223</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1621,6 +1661,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55925918</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1723,8 +1768,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122589604</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>